--- a/outputs/48588.xlsx
+++ b/outputs/48588.xlsx
@@ -364,7 +364,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A2,$A$2:A2))</f>
+        <f aca="false">MATCH(A2,$A$2:A$43,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -373,7 +373,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A3,$A$2:A3))</f>
+        <f aca="false">MATCH(A3,$A$2:A$43,0)</f>
         <v>2</v>
       </c>
     </row>
@@ -382,7 +382,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A4,$A$2:A4))</f>
+        <f aca="false">MATCH(A4,$A$2:A$43,0)</f>
         <v>3</v>
       </c>
     </row>
@@ -391,7 +391,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A5,$A$2:A5))</f>
+        <f aca="false">MATCH(A5,$A$2:A$43,0)</f>
         <v>4</v>
       </c>
     </row>
@@ -400,7 +400,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A6,$A$2:A6))</f>
+        <f aca="false">MATCH(A6,$A$2:A$43,0)</f>
         <v>5</v>
       </c>
     </row>
@@ -409,7 +409,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A7,$A$2:A7))</f>
+        <f aca="false">MATCH(A7,$A$2:A$43,0)</f>
         <v>6</v>
       </c>
     </row>
@@ -418,7 +418,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A8,$A$2:A8))</f>
+        <f aca="false">MATCH(A8,$A$2:A$43,0)</f>
         <v>7</v>
       </c>
     </row>
@@ -427,7 +427,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A9,$A$2:A9))</f>
+        <f aca="false">MATCH(A9,$A$2:A$43,0)</f>
         <v>8</v>
       </c>
     </row>
@@ -436,7 +436,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A10,$A$2:A10))</f>
+        <f aca="false">MATCH(A10,$A$2:A$43,0)</f>
         <v>9</v>
       </c>
     </row>
@@ -445,8 +445,8 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A11,$A$2:A11))</f>
-        <v>9</v>
+        <f aca="false">MATCH(A11,$A$2:A$43,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -454,8 +454,8 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A12,$A$2:A12))</f>
-        <v>9</v>
+        <f aca="false">MATCH(A12,$A$2:A$43,0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -463,8 +463,8 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A13,$A$2:A13))</f>
-        <v>10</v>
+        <f aca="false">MATCH(A13,$A$2:A$43,0)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -472,8 +472,8 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A14,$A$2:A14))</f>
-        <v>10</v>
+        <f aca="false">MATCH(A14,$A$2:A$43,0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -481,8 +481,8 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A15,$A$2:A15))</f>
-        <v>11</v>
+        <f aca="false">MATCH(A15,$A$2:A$43,0)</f>
+        <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -490,8 +490,8 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A16,$A$2:A16))</f>
-        <v>11</v>
+        <f aca="false">MATCH(A16,$A$2:A$43,0)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -499,8 +499,8 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A17,$A$2:A17))</f>
-        <v>12</v>
+        <f aca="false">MATCH(A17,$A$2:A$43,0)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -508,8 +508,8 @@
         <v>6</v>
       </c>
       <c r="B18" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A18,$A$2:A18))</f>
-        <v>12</v>
+        <f aca="false">MATCH(A18,$A$2:A$43,0)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -517,8 +517,8 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A19,$A$2:A19))</f>
-        <v>13</v>
+        <f aca="false">MATCH(A19,$A$2:A$43,0)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -526,8 +526,8 @@
         <v>7</v>
       </c>
       <c r="B20" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A20,$A$2:A20))</f>
-        <v>13</v>
+        <f aca="false">MATCH(A20,$A$2:A$43,0)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -535,8 +535,8 @@
         <v>15</v>
       </c>
       <c r="B21" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A21,$A$2:A21))</f>
-        <v>14</v>
+        <f aca="false">MATCH(A21,$A$2:A$43,0)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -544,8 +544,8 @@
         <v>8</v>
       </c>
       <c r="B22" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A22,$A$2:A22))</f>
-        <v>14</v>
+        <f aca="false">MATCH(A22,$A$2:A$43,0)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -553,8 +553,8 @@
         <v>16</v>
       </c>
       <c r="B23" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A23,$A$2:A23))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A23,$A$2:A$43,0)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -562,8 +562,8 @@
         <v>2</v>
       </c>
       <c r="B24" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A24,$A$2:A24))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A24,$A$2:A$43,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -571,8 +571,8 @@
         <v>3</v>
       </c>
       <c r="B25" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A25,$A$2:A25))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A25,$A$2:A$43,0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -580,8 +580,8 @@
         <v>4</v>
       </c>
       <c r="B26" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A26,$A$2:A26))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A26,$A$2:A$43,0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -589,8 +589,8 @@
         <v>5</v>
       </c>
       <c r="B27" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A27,$A$2:A27))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A27,$A$2:A$43,0)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -598,8 +598,8 @@
         <v>6</v>
       </c>
       <c r="B28" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A28,$A$2:A28))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A28,$A$2:A$43,0)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -607,8 +607,8 @@
         <v>7</v>
       </c>
       <c r="B29" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A29,$A$2:A29))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A29,$A$2:A$43,0)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -616,8 +616,8 @@
         <v>8</v>
       </c>
       <c r="B30" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A30,$A$2:A30))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A30,$A$2:A$43,0)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -625,8 +625,8 @@
         <v>9</v>
       </c>
       <c r="B31" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A31,$A$2:A31))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A31,$A$2:A$43,0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -634,8 +634,8 @@
         <v>10</v>
       </c>
       <c r="B32" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A32,$A$2:A32))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A32,$A$2:A$43,0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -643,8 +643,8 @@
         <v>11</v>
       </c>
       <c r="B33" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A33,$A$2:A33))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A33,$A$2:A$43,0)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -652,8 +652,8 @@
         <v>12</v>
       </c>
       <c r="B34" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A34,$A$2:A34))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A34,$A$2:A$43,0)</f>
+        <v>14</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -661,8 +661,8 @@
         <v>13</v>
       </c>
       <c r="B35" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A35,$A$2:A35))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A35,$A$2:A$43,0)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -670,8 +670,8 @@
         <v>14</v>
       </c>
       <c r="B36" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A36,$A$2:A36))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A36,$A$2:A$43,0)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -679,8 +679,8 @@
         <v>15</v>
       </c>
       <c r="B37" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A37,$A$2:A37))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A37,$A$2:A$43,0)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -688,8 +688,8 @@
         <v>16</v>
       </c>
       <c r="B38" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A38,$A$2:A38))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A38,$A$2:A$43,0)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -697,8 +697,8 @@
         <v>8</v>
       </c>
       <c r="B39" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A39,$A$2:A39))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A39,$A$2:A$43,0)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -706,8 +706,8 @@
         <v>9</v>
       </c>
       <c r="B40" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A40,$A$2:A40))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A40,$A$2:A$43,0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -715,8 +715,8 @@
         <v>10</v>
       </c>
       <c r="B41" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A41,$A$2:A41))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A41,$A$2:A$43,0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -724,8 +724,8 @@
         <v>11</v>
       </c>
       <c r="B42" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A42,$A$2:A42))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A42,$A$2:A$43,0)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -733,8 +733,8 @@
         <v>12</v>
       </c>
       <c r="B43" s="1" t="n">
-        <f aca="false">SUMPRODUCT(1/COUNTIF($A$2:A43,$A$2:A43))</f>
-        <v>15</v>
+        <f aca="false">MATCH(A43,$A$2:A$43,0)</f>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
